--- a/blueboot_agency_power_agent/output/agency_leads.xlsx
+++ b/blueboot_agency_power_agent/output/agency_leads.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA17"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1282,86 +1282,86 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>probeyservices_com</t>
+          <t>www_webi_tn</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Probeyservices</t>
+          <t>Webi</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>probeyservices.com</t>
+          <t>webi.tn</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://probeyservices.com/</t>
+          <t>https://www.webi.tn/</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sortlist NO – content marketing</t>
+          <t>Sortlist TN – web design</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Probey Services | Professional Web Design &amp; App Development</t>
+          <t>WEBI - Agence Web Tunisie | Création Sites &amp; SEO depuis 2011</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Top- rated among the best in the industry on DesignRush, Probey Services delivers exceptional web design, mobile apps, and digital marketing services to help businesses thrive globally.</t>
+          <t>Agence web Tunisie spécialisée en création de sites WordPress, e-commerce et SEO. +14 ans d'expérience. Devis gratuit sous 24h.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>hr@probeyservices.com, info@probeyservices.com, service@probeyservices.com</t>
+          <t>contact@webi.tn, nom@entreprise.com, webitunisie@gmail.com</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t xml:space="preserve">, , </t>
+          <t xml:space="preserve">, , founder": { "@type": "Person", "name": "Feriel Mathlouthi", </t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t xml:space="preserve">, +91 97739 01990, </t>
+          <t xml:space="preserve">+216 20 260 428, +216 27 707 777, </t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t xml:space="preserve">, Probey Services, </t>
+          <t xml:space="preserve">Agence Web Tunisie, Réalisations Web, </t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+1 202-847-6988, +1 202-995-7212, +44 7537 188459, +61 485 921 488, +91 97739 01990</t>
+          <t>+216 27 337 777, +216 27 707 777</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://probeyservices.com/contact-us/</t>
+          <t>https://webi.tn/contact/</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/probeyservices/mycompany/</t>
+          <t>https://www.linkedin.com/company/webi/</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>elementor, magento, woocommerce, wordpress</t>
+          <t>prestashop, woocommerce, wordpress</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>ai_interest, communication, public_sector, seo, web_agency, wordpress</t>
+          <t>ai_interest, communication, seo, web_agency, wordpress</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>web_agency: web design, website; wordpress: wordpress, wp-content, woocommerce, elementor; seo: seo, google ads; communication: content; public_sector: stat; ai_interest: ai, ki; has services/customers/cases language; offers maintenance/support; agency language: partner; NON-AGENCY penalty (real estate): -30</t>
+          <t>web_agency: agence web, web design, développement web, site web; wordpress: wordpress, wp-content, woocommerce; seo: seo, référencement, visibilité, optimisation; communication: agence de communication, communication, contenu, content; ai_interest: intelligence artificielle, ia, ai, automatisation; has services/customers/cases language; offers maintenance/support; agency language: nous développons, nos clients, références</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1385,18 +1385,18 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-25T10:08:58+00:00</t>
+          <t>2026-05-25T10:24:14+00:00</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr"/>
@@ -1409,50 +1409,78 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>www_facebook_com</t>
+          <t>labgrowth_com_br</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Labgrowth</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>Labgrowth.com.br</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/</t>
+          <t>https://Labgrowth.com.br/</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sitecore Partner Finder</t>
+          <t>Sortlist BR – SEO</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Facebook</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+          <t>Agência de Marketing Digital em Curitiba | Lab Growth</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Agência de Marketing Digital em Curitiba | Lab Growth – Estratégias de alto impacto para escalar a geração de leads e vendas do seu negócio.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>contato@labgrowth.com.br</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>+55 41 99550-5702</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Gravity Forms</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>+55 41 99550-5702</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lab-growth/</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>elementor, wordpress</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>ai_interest, communication, public_sector, seo, wordpress</t>
+          <t>ai_interest, communication, seo, web_agency, wordpress</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -1461,7 +1489,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>wordpress: divi; seo: seo; communication: content; public_sector: stat; ai_interest: ai, ki; has services/customers/cases language; offers maintenance/support</t>
+          <t>web_agency: criação de sites, web design, desenvolvimento de sites; wordpress: wordpress, wp-content, elementor, divi; seo: seo, otimização para motores de busca, google ads; communication: marketing de conteúdo, social media; ai_interest: ia, ai, automação; has services/customers/cases language; offers maintenance/support; agency language: desenvolvemos, nossos clientes, cases de sucesso</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1476,18 +1504,18 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>BR</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-25T10:08:54+00:00</t>
+          <t>2026-05-25T10:25:33+00:00</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr"/>
@@ -1500,66 +1528,86 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>quantumitinnovation_com</t>
+          <t>probeyservices_com</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quantumitinnovation</t>
+          <t>Probeyservices</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>quantumitinnovation.com</t>
+          <t>probeyservices.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://quantumitinnovation.com/</t>
+          <t>https://probeyservices.com/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sortlist IE – content marketing</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
+          <t>Sortlist NO – content marketing</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Probey Services | Professional Web Design &amp; App Development</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Top- rated among the best in the industry on DesignRush, Probey Services delivers exceptional web design, mobile apps, and digital marketing services to help businesses thrive globally.</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>sales@quantumitinnovation.com</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>hr@probeyservices.com, info@probeyservices.com, service@probeyservices.com</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">, , </t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>+1 213-341-0348</t>
+          <t xml:space="preserve">, +91 97739 01990, </t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Columbine Ln</t>
+          <t xml:space="preserve">, Probey Services, </t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+1 213-341-0348, +1 587-603-6054, +1 877-877-3644, +353 21 878 736, +353 94 070 6804, +61 3 7042 4786, +91 97179 98517</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>+1 202-847-6988, +1 202-995-7212, +44 7537 188459, +61 485 921 488, +91 97739 01990</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>https://probeyservices.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/probeyservices/mycompany/</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>nextjs</t>
+          <t>elementor, magento, woocommerce, wordpress</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>ai_interest, communication, seo, web_agency</t>
+          <t>ai_interest, communication, public_sector, seo, web_agency, wordpress</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1568,7 +1616,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>web_agency: web development; seo: visibility; communication: content; ai_interest: ai; has services/customers/cases language</t>
+          <t>web_agency: web design, website; wordpress: wordpress, wp-content, woocommerce, elementor; seo: seo, google ads; communication: content; public_sector: stat; ai_interest: ai, ki; has services/customers/cases language; offers maintenance/support; agency language: partner; NON-AGENCY penalty (real estate): -30</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1583,18 +1631,18 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="X10" t="inlineStr"/>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-25T10:15:14+00:00</t>
+          <t>2026-05-25T10:08:58+00:00</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr"/>
@@ -1607,22 +1655,22 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>www_youtube_com</t>
+          <t>www_facebook_com</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Youtube</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>youtube.com</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/</t>
+          <t>https://www.facebook.com/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1632,33 +1680,25 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Med YouTube kan du se populære videoer, kose deg med favorittmusikken din og laste opp ditt eget innhold – og dele det med familie, venner og resten av verden.</t>
-        </is>
-      </c>
+          <t>Facebook</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>https://www.youtube.com/about/</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>ai_interest, communication, public_sector, wordpress</t>
+          <t>ai_interest, communication, public_sector, seo, wordpress</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -1667,7 +1707,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>wordpress: divi; communication: innhold, content; public_sector: stat; ai_interest: ai, ki; has services/customers/cases language; offers maintenance/support</t>
+          <t>wordpress: divi; seo: seo; communication: content; public_sector: stat; ai_interest: ai, ki; has services/customers/cases language; offers maintenance/support</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
@@ -1693,7 +1733,7 @@
       <c r="X11" t="inlineStr"/>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-25T10:08:57+00:00</t>
+          <t>2026-05-25T10:08:54+00:00</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr"/>
@@ -1706,75 +1746,75 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>www_debottomline_be</t>
+          <t>quantumitinnovation_com</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Debottomline</t>
+          <t>Quantumitinnovation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>deBottomline.be</t>
+          <t>quantumitinnovation.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.deBottomline.be/</t>
+          <t>https://quantumitinnovation.com/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sortlist BE – digital agencies</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>deBottomline</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Achter elke groeivraag zit een vertrouwensvraag. Hoe overtuig je een klant, sollicitant of collega om voor jou te kiezen? Wij helpen je dat vertrouwen op te bouwen met communicatie die vertrekt vanuit jouw verhaal.</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>Sortlist IE – content marketing</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>sales@quantumitinnovation.com</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>https://www.deBottomline.be/contact</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/2898418/admin/page-posts/published/</t>
-        </is>
-      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>+1 213-341-0348</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Columbine Ln</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>+1 213-341-0348, +1 587-603-6054, +1 877-877-3644, +353 21 878 736, +353 94 070 6804, +61 3 7042 4786, +91 97179 98517</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr">
         <is>
-          <t>webflow</t>
+          <t>nextjs</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>ai_interest, communication, web_agency</t>
+          <t>ai_interest, communication, seo, web_agency</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>web_agency: website; communication: content; ai_interest: ai; has services/customers/cases language; agency language: onze klanten</t>
+          <t>web_agency: web development; seo: visibility; communication: content; ai_interest: ai; has services/customers/cases language</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1789,18 +1829,18 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-25T10:12:19+00:00</t>
+          <t>2026-05-25T10:15:14+00:00</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr"/>
@@ -1813,83 +1853,67 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>www_bfenterprise_it</t>
+          <t>www_youtube_com</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Bfenterprise</t>
+          <t>Youtube</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>bfenterprise.it</t>
+          <t>youtube.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.bfenterprise.it/</t>
+          <t>https://www.youtube.com/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sortlist IT – web design</t>
+          <t>Sitecore Partner Finder</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Agenzia di Marketing per la visibilità online | BFENTERPRISE</t>
+          <t>YouTube</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Siamo l'Agenzia di Marketing specializzata nell'aumento della visibilità online, curiamo il tuo brand come in una botique per raggiungere i tuoi obiettivi insieme</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>info@bfenterprise.it</t>
-        </is>
-      </c>
+          <t>Med YouTube kan du se populære videoer, kose deg med favorittmusikken din og laste opp ditt eget innhold – og dele det med familie, venner og resten av verden.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>+39 049 490 6614</t>
-        </is>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>+39 049 490 6614, +39 0525 308 0286</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/bfenterprise/</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>wordpress</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/about/</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>ai_interest, communication, seo, web_agency, wordpress</t>
+          <t>ai_interest, communication, public_sector, wordpress</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>web_agency: sito web, siti web; wordpress: wordpress, wp-content, divi; seo: seo, google ads, visibilità; communication: agenzia di comunicazione, comunicazione, content; ai_interest: ia, ai; has services/customers/cases language; offers maintenance/support; agency language: referenze, case study, partner; NON-AGENCY penalty (bar, medico): -60</t>
+          <t>wordpress: divi; communication: innhold, content; public_sector: stat; ai_interest: ai, ki; has services/customers/cases language; offers maintenance/support</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1904,18 +1928,18 @@
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-25T10:17:15+00:00</t>
+          <t>2026-05-25T10:08:57+00:00</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr"/>
@@ -1928,77 +1952,57 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>uinno_io</t>
+          <t>www_debottomline_be</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Uinno</t>
+          <t>Debottomline</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>uinno.io</t>
+          <t>deBottomline.be</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://uinno.io/</t>
+          <t>https://www.deBottomline.be/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sortlist EE – web development</t>
+          <t>Sortlist BE – digital agencies</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Uinno: Software Development Partner</t>
+          <t>deBottomline</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Award winning software development partner delivering custom AI solutions, tech teams, and consulting.</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>contact@uinno.io, hr@uinno.io</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Co-Founder &amp;amp; CRO Strategist who keeps numbers and vision, </t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>+372 455 9991, +372 455 9991</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Attach Files, Attach Files</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>+372 455 9991</t>
-        </is>
-      </c>
+          <t>Achter elke groeivraag zit een vertrouwensvraag. Hoe overtuig je een klant, sollicitant of collega om voor jou te kiezen? Wij helpen je dat vertrouwen op te bouwen met communicatie die vertrekt vanuit jouw verhaal.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://uinno.io/about-uinno</t>
+          <t>https://www.deBottomline.be/contact</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/uinno</t>
+          <t>https://www.linkedin.com/company/2898418/admin/page-posts/published/</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>gatsby, webflow</t>
+          <t>webflow</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2007,7 +2011,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -2016,7 +2020,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>web_agency: web design, website; communication: content; ai_interest: ai, chatgpt; agency language: partner</t>
+          <t>web_agency: website; communication: content; ai_interest: ai; has services/customers/cases language; agency language: onze klanten</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -2031,18 +2035,18 @@
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-25T10:20:10+00:00</t>
+          <t>2026-05-25T10:12:19+00:00</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr"/>
@@ -2055,95 +2059,83 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>vrijdagonline_nl</t>
+          <t>www_bfenterprise_it</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vrijdagonline</t>
+          <t>Bfenterprise</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>vrijdagonline.nl</t>
+          <t>bfenterprise.it</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://vrijdagonline.nl/</t>
+          <t>https://www.bfenterprise.it/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sortlist NL – web development</t>
+          <t>Sortlist IT – web design</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maatwerk Umbraco Website vanaf €2.250 | VrijdagOnline</t>
+          <t>Agenzia di Marketing per la visibilità online | BFENTERPRISE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Laat een Maatwerk Umbraco Website bouwen vanaf €2.250. Strategisch design, SEO en ontwikkeling voor maximale conversie en groei.</t>
+          <t>Siamo l'Agenzia di Marketing specializzata nell'aumento della visibilità online, curiamo il tuo brand come in una botique per raggiungere i tuoi obiettivi insieme</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>sales@vrijdagonline.nl, service@vrijdagonline.nl, tjitte@vrijdagonline.nl</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>, , Consultant Bel: 06-15223608</t>
-        </is>
-      </c>
+          <t>info@bfenterprise.it</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t xml:space="preserve">+31 50 211 5975, +31 50 230 9815, </t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>, , Tjitte Hogeterp</t>
-        </is>
-      </c>
+          <t>+39 049 490 6614</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+31 50 211 5975, +31 50 230 9815, +31 6 15223608</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>https://vrijdagonline.nl/contact</t>
-        </is>
-      </c>
+          <t>+39 049 490 6614, +39 0525 308 0286</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vrijdagonline-</t>
+          <t>https://www.linkedin.com/company/bfenterprise/</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>umbraco</t>
+          <t>wordpress</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>ai_interest, communication, public_sector, seo, web_agency</t>
+          <t>ai_interest, communication, seo, web_agency, wordpress</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>web_agency: webdesign, webontwikkeling, website, website bouwen; seo: seo, google ads, zichtbaarheid; communication: communicatie, content; public_sector: zorg; ai_interest: ai; has services/customers/cases language; offers maintenance/support; agency language: wij ontwikkelen, partner, portfolio; NON-AGENCY penalty (bank, bar): -60</t>
+          <t>web_agency: sito web, siti web; wordpress: wordpress, wp-content, divi; seo: seo, google ads, visibilità; communication: agenzia di comunicazione, comunicazione, content; ai_interest: ia, ai; has services/customers/cases language; offers maintenance/support; agency language: referenze, case study, partner; NON-AGENCY penalty (bar, medico): -60</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -2158,18 +2150,18 @@
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-25T10:11:48+00:00</t>
+          <t>2026-05-25T10:17:15+00:00</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr"/>
@@ -2182,73 +2174,77 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>www_estudiowuala_com</t>
+          <t>uinno_io</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Estudiowuala</t>
+          <t>Uinno</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>estudiowuala.com</t>
+          <t>uinno.io</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.estudiowuala.com/</t>
+          <t>https://uinno.io/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sortlist EE – web design</t>
+          <t>Sortlist EE – web development</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Estudio Wüala</t>
+          <t>Uinno: Software Development Partner</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Convertimos SaaS complejos en experiencias simples en solo 1-2 semanas. Especialistas en Conversion Sprints y diseño UX estratégico para startups que necesitan resultados rápidos y sin fricción.</t>
+          <t>Award winning software development partner delivering custom AI solutions, tech teams, and consulting.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>hello@framer.com, hola@estudiowuala.com</t>
+          <t>contact@uinno.io, hr@uinno.io</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t xml:space="preserve">Co-Founder &amp;amp; CRO Strategist who keeps numbers and vision, </t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t xml:space="preserve">, </t>
+          <t>+372 455 9991, +372 455 9991</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>, Satoshi Placeholder</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>Attach Files, Attach Files</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>+372 455 9991</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://www.estudiowuala.com/contact</t>
+          <t>https://uinno.io/about-uinno</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/estudio-w%C3%BCala/</t>
+          <t>https://www.linkedin.com/company/uinno</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>framer, webflow</t>
+          <t>gatsby, webflow</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2257,16 +2253,16 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>web_agency: website; communication: content; ai_interest: ai</t>
+          <t>web_agency: web design, website; communication: content; ai_interest: ai, chatgpt; agency language: partner</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
@@ -2292,7 +2288,7 @@
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-25T10:20:08+00:00</t>
+          <t>2026-05-25T10:20:10+00:00</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr"/>
@@ -2305,70 +2301,86 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>non_linear_studio</t>
+          <t>vrijdagonline_nl</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Non Linear</t>
+          <t>Vrijdagonline</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>non-linear.studio</t>
+          <t>vrijdagonline.nl</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://non-linear.studio/</t>
+          <t>https://vrijdagonline.nl/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sortlist EE – web design</t>
+          <t>Sortlist NL – web development</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Non-Linear Studio — Design Studio Building Tomorrow’s Brands</t>
+          <t>Maatwerk Umbraco Website vanaf €2.250 | VrijdagOnline</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Independent creative studio crafting digital experiences connecting design and technology, with offices in New York City, the Wasatch Mountains of Utah and the Baltic Sea in Tallinn.</t>
+          <t>Laat een Maatwerk Umbraco Website bouwen vanaf €2.250. Strategisch design, SEO en ontwikkeling voor maximale conversie en groei.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>hello@non-linear.studio</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
+          <t>sales@vrijdagonline.nl, service@vrijdagonline.nl, tjitte@vrijdagonline.nl</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>, , Consultant Bel: 06-15223608</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">+31 50 211 5975, +31 50 230 9815, </t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>, , Tjitte Hogeterp</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>+31 50 211 5975, +31 50 230 9815, +31 6 15223608</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://non-linear.studio/contact</t>
+          <t>https://vrijdagonline.nl/contact</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/non-linear-studio/</t>
+          <t>https://www.linkedin.com/company/vrijdagonline-</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>sanity</t>
+          <t>umbraco</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>ai_interest, communication, web_agency</t>
+          <t>ai_interest, communication, public_sector, seo, web_agency</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -2377,7 +2389,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>web_agency: website; communication: content; ai_interest: ai</t>
+          <t>web_agency: webdesign, webontwikkeling, website, website bouwen; seo: seo, google ads, zichtbaarheid; communication: communicatie, content; public_sector: zorg; ai_interest: ai; has services/customers/cases language; offers maintenance/support; agency language: wij ontwikkelen, partner, portfolio; NON-AGENCY penalty (bank, bar): -60</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -2392,22 +2404,256 @@
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-05-25T10:20:09+00:00</t>
+          <t>2026-05-25T10:11:48+00:00</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>www_estudiowuala_com</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Estudiowuala</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>estudiowuala.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>https://www.estudiowuala.com/</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sortlist EE – web design</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Estudio Wüala</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Convertimos SaaS complejos en experiencias simples en solo 1-2 semanas. Especialistas en Conversion Sprints y diseño UX estratégico para startups que necesitan resultados rápidos y sin fricción.</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>hello@framer.com, hola@estudiowuala.com</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">, </t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">, </t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>, Satoshi Placeholder</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>https://www.estudiowuala.com/contact</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/estudio-w%C3%BCala/</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>framer, webflow</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>ai_interest, communication, web_agency</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>51</v>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>C - Maybe</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>web_agency: website; communication: content; ai_interest: ai</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Focus on public-information sites: help visitors find answers across pages, PDFs and articles.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-25T10:20:08+00:00</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>non_linear_studio</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Non Linear</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>non-linear.studio</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://non-linear.studio/</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sortlist EE – web design</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Non-Linear Studio — Design Studio Building Tomorrow’s Brands</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Independent creative studio crafting digital experiences connecting design and technology, with offices in New York City, the Wasatch Mountains of Utah and the Baltic Sea in Tallinn.</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>hello@non-linear.studio</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>https://non-linear.studio/contact</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/non-linear-studio/</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>sanity</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>ai_interest, communication, web_agency</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>51</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>C - Maybe</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>web_agency: website; communication: content; ai_interest: ai</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Focus on public-information sites: help visitors find answers across pages, PDFs and articles.</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-25T10:20:09+00:00</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
@@ -2424,7 +2670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -2439,7 +2685,7 @@
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
     <col width="55" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2936,27 +3182,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>probeyservices_com</t>
+          <t>www_webi_tn</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Probeyservices</t>
+          <t>Webi</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>probeyservices.com</t>
+          <t>webi.tn</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://probeyservices.com/</t>
+          <t>https://www.webi.tn/</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2965,51 +3211,59 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/probeyservices/mycompany/</t>
+          <t>https://www.linkedin.com/company/webi/</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://probeyservices.com/contact-us/</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+          <t>https://webi.tn/contact/</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Agence Web Tunisie</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>hr@probeyservices.com</t>
+          <t>contact@webi.tn</t>
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>+216 20 260 428</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>probeyservices_com</t>
+          <t>www_webi_tn</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Probeyservices</t>
+          <t>Webi</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>probeyservices.com</t>
+          <t>webi.tn</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://probeyservices.com/</t>
+          <t>https://www.webi.tn/</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3018,59 +3272,59 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/probeyservices/mycompany/</t>
+          <t>https://www.linkedin.com/company/webi/</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://probeyservices.com/contact-us/</t>
+          <t>https://webi.tn/contact/</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Probey Services</t>
+          <t>Réalisations Web</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>info@probeyservices.com</t>
+          <t>nom@entreprise.com</t>
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+91 97739 01990</t>
+          <t>+216 27 707 777</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>probeyservices_com</t>
+          <t>www_webi_tn</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Probeyservices</t>
+          <t>Webi</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>probeyservices.com</t>
+          <t>webi.tn</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://probeyservices.com/</t>
+          <t>https://www.webi.tn/</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Tunisia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -3079,51 +3333,55 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/probeyservices/mycompany/</t>
+          <t>https://www.linkedin.com/company/webi/</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://probeyservices.com/contact-us/</t>
+          <t>https://webi.tn/contact/</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
-          <t>service@probeyservices.com</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr"/>
+          <t>webitunisie@gmail.com</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>founder": { "@type": "Person"</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>www_facebook_com</t>
+          <t>labgrowth_com_br</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Facebook</t>
+          <t>Labgrowth</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>facebook.com</t>
+          <t>Labgrowth.com.br</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/</t>
+          <t>https://Labgrowth.com.br/</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3132,39 +3390,55 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>93</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/lab-growth/</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Gravity Forms</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>contato@labgrowth.com.br</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>+55 41 99550-5702</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>quantumitinnovation_com</t>
+          <t>probeyservices_com</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Quantumitinnovation</t>
+          <t>Probeyservices</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>quantumitinnovation.com</t>
+          <t>probeyservices.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://quantumitinnovation.com/</t>
+          <t>https://probeyservices.com/</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3173,46 +3447,46 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>77</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Columbine Ln</t>
-        </is>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/probeyservices/mycompany/</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>https://probeyservices.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>sales@quantumitinnovation.com</t>
+          <t>hr@probeyservices.com</t>
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>+1 213-341-0348</t>
-        </is>
-      </c>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>www_youtube_com</t>
+          <t>probeyservices_com</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Youtube</t>
+          <t>Probeyservices</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>youtube.com</t>
+          <t>probeyservices.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/</t>
+          <t>https://probeyservices.com/</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3226,441 +3500,413 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>75</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/probeyservices/mycompany/</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/about/</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+          <t>https://probeyservices.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Probey Services</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>info@probeyservices.com</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>+91 97739 01990</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>www_debottomline_be</t>
+          <t>probeyservices_com</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Debottomline</t>
+          <t>Probeyservices</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>deBottomline.be</t>
+          <t>probeyservices.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.deBottomline.be/</t>
+          <t>https://probeyservices.com/</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/2898418/admin/page-posts/published/</t>
+          <t>https://www.linkedin.com/company/probeyservices/mycompany/</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.deBottomline.be/contact</t>
+          <t>https://probeyservices.com/contact-us/</t>
         </is>
       </c>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>service@probeyservices.com</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>www_bfenterprise_it</t>
+          <t>www_facebook_com</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Bfenterprise</t>
+          <t>Facebook</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>bfenterprise.it</t>
+          <t>facebook.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.bfenterprise.it/</t>
+          <t>https://www.facebook.com/</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>68</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/bfenterprise/</t>
-        </is>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>info@bfenterprise.it</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>+39 049 490 6614</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>uinno_io</t>
+          <t>quantumitinnovation_com</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Uinno</t>
+          <t>Quantumitinnovation</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>uinno.io</t>
+          <t>quantumitinnovation.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://uinno.io/</t>
+          <t>https://quantumitinnovation.com/</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>61</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/uinno</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>https://uinno.io/about-uinno</t>
-        </is>
-      </c>
+        <v>77</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Attach Files</t>
+          <t>Columbine Ln</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>contact@uinno.io</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Co-Founder &amp;amp; CRO Strategist who keeps numbers and vision</t>
-        </is>
-      </c>
+          <t>sales@quantumitinnovation.com</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+372 455 9991</t>
+          <t>+1 213-341-0348</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>uinno_io</t>
+          <t>www_youtube_com</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Uinno</t>
+          <t>Youtube</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>uinno.io</t>
+          <t>youtube.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://uinno.io/</t>
+          <t>https://www.youtube.com/</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>B - Good fit</t>
+          <t>A - High fit</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>61</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>https://www.linkedin.com/company/uinno</t>
-        </is>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://uinno.io/about-uinno</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Attach Files</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>hr@uinno.io</t>
-        </is>
-      </c>
+          <t>https://www.youtube.com/about/</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>+372 455 9991</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>vrijdagonline_nl</t>
+          <t>www_debottomline_be</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Vrijdagonline</t>
+          <t>Debottomline</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>vrijdagonline.nl</t>
+          <t>deBottomline.be</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://vrijdagonline.nl/</t>
+          <t>https://www.deBottomline.be/</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Belgium</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vrijdagonline-</t>
+          <t>https://www.linkedin.com/company/2898418/admin/page-posts/published/</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://vrijdagonline.nl/contact</t>
+          <t>https://www.deBottomline.be/contact</t>
         </is>
       </c>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>sales@vrijdagonline.nl</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>+31 50 211 5975</t>
-        </is>
-      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>vrijdagonline_nl</t>
+          <t>www_bfenterprise_it</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Vrijdagonline</t>
+          <t>Bfenterprise</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>vrijdagonline.nl</t>
+          <t>bfenterprise.it</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://vrijdagonline.nl/</t>
+          <t>https://www.bfenterprise.it/</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>53</v>
+        <v>68</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vrijdagonline-</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>https://vrijdagonline.nl/contact</t>
-        </is>
-      </c>
+          <t>https://www.linkedin.com/company/bfenterprise/</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>service@vrijdagonline.nl</t>
+          <t>info@bfenterprise.it</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+31 50 230 9815</t>
+          <t>+39 049 490 6614</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>vrijdagonline_nl</t>
+          <t>uinno_io</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Vrijdagonline</t>
+          <t>Uinno</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>vrijdagonline.nl</t>
+          <t>uinno.io</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://vrijdagonline.nl/</t>
+          <t>https://uinno.io/</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Estonia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/vrijdagonline-</t>
+          <t>https://www.linkedin.com/company/uinno</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://vrijdagonline.nl/contact</t>
+          <t>https://uinno.io/about-uinno</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Tjitte Hogeterp</t>
+          <t>Attach Files</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>tjitte@vrijdagonline.nl</t>
+          <t>contact@uinno.io</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Consultant Bel: 06-15223608</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
+          <t>Co-Founder &amp;amp; CRO Strategist who keeps numbers and vision</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>+372 455 9991</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>www_estudiowuala_com</t>
+          <t>uinno_io</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Estudiowuala</t>
+          <t>Uinno</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>estudiowuala.com</t>
+          <t>uinno.io</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.estudiowuala.com/</t>
+          <t>https://uinno.io/</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3670,55 +3916,63 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>C - Maybe</t>
+          <t>B - Good fit</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/estudio-w%C3%BCala/</t>
+          <t>https://www.linkedin.com/company/uinno</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.estudiowuala.com/contact</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+          <t>https://uinno.io/about-uinno</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Attach Files</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>hello@framer.com</t>
+          <t>hr@uinno.io</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>+372 455 9991</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>www_estudiowuala_com</t>
+          <t>vrijdagonline_nl</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Estudiowuala</t>
+          <t>Vrijdagonline</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>estudiowuala.com</t>
+          <t>vrijdagonline.nl</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.estudiowuala.com/</t>
+          <t>https://vrijdagonline.nl/</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3727,55 +3981,55 @@
         </is>
       </c>
       <c r="G24" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/estudio-w%C3%BCala/</t>
+          <t>https://www.linkedin.com/company/vrijdagonline-</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.estudiowuala.com/contact</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Satoshi Placeholder</t>
-        </is>
-      </c>
+          <t>https://vrijdagonline.nl/contact</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>hola@estudiowuala.com</t>
+          <t>sales@vrijdagonline.nl</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>+31 50 211 5975</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>non_linear_studio</t>
+          <t>vrijdagonline_nl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Non Linear</t>
+          <t>Vrijdagonline</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>non-linear.studio</t>
+          <t>vrijdagonline.nl</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://non-linear.studio/</t>
+          <t>https://vrijdagonline.nl/</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3784,26 +4038,254 @@
         </is>
       </c>
       <c r="G25" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.linkedin.com/company/non-linear-studio/</t>
+          <t>https://www.linkedin.com/company/vrijdagonline-</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://non-linear.studio/contact</t>
+          <t>https://vrijdagonline.nl/contact</t>
         </is>
       </c>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
+          <t>service@vrijdagonline.nl</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>+31 50 230 9815</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>vrijdagonline_nl</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Vrijdagonline</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>vrijdagonline.nl</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://vrijdagonline.nl/</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>C - Maybe</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>53</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vrijdagonline-</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>https://vrijdagonline.nl/contact</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Tjitte Hogeterp</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>tjitte@vrijdagonline.nl</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Consultant Bel: 06-15223608</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>www_estudiowuala_com</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Estudiowuala</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>estudiowuala.com</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://www.estudiowuala.com/</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>C - Maybe</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>51</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/estudio-w%C3%BCala/</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>https://www.estudiowuala.com/contact</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>hello@framer.com</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>www_estudiowuala_com</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Estudiowuala</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>estudiowuala.com</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://www.estudiowuala.com/</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>C - Maybe</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>51</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/estudio-w%C3%BCala/</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>https://www.estudiowuala.com/contact</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Satoshi Placeholder</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>hola@estudiowuala.com</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>non_linear_studio</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Non Linear</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>non-linear.studio</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://non-linear.studio/</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>C - Maybe</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>51</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/non-linear-studio/</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>https://non-linear.studio/contact</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>hello@non-linear.studio</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3838,7 +4320,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
@@ -3848,7 +4330,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -3858,7 +4340,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5">
@@ -3868,7 +4350,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -3879,7 +4361,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-05-25T12:20:11</t>
+          <t>2026-05-25T12:27:07</t>
         </is>
       </c>
     </row>
